--- a/Alta Masiva Productos.xlsx
+++ b/Alta Masiva Productos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="27945" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -338,7 +338,7 @@
     <numFmt numFmtId="178" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="0_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,13 +348,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -881,146 +874,146 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1038,12 +1031,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1059,7 +1052,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1432,7 +1425,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="9">
         <v>1</v>
@@ -1467,7 +1460,7 @@
         <v>12</v>
       </c>
       <c r="D3" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" s="9">
         <v>1</v>
@@ -1502,7 +1495,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" s="9">
         <v>1</v>
@@ -1537,7 +1530,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" s="9">
         <v>1</v>
@@ -1572,7 +1565,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" s="9">
         <v>1</v>
@@ -1607,7 +1600,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" s="9">
         <v>1</v>
@@ -1642,13 +1635,13 @@
         <v>18</v>
       </c>
       <c r="D8" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="9">
         <v>1</v>
       </c>
-      <c r="F8">
-        <v>26</v>
+      <c r="F8" s="9">
+        <v>25</v>
       </c>
       <c r="G8" s="9">
         <v>33553.98</v>
@@ -1677,13 +1670,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" s="9">
         <v>1</v>
       </c>
-      <c r="F9">
-        <v>26</v>
+      <c r="F9" s="9">
+        <v>25</v>
       </c>
       <c r="G9" s="9">
         <v>46436.32</v>
@@ -1712,13 +1705,13 @@
         <v>22</v>
       </c>
       <c r="D10" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" s="9">
         <v>1</v>
       </c>
-      <c r="F10">
-        <v>26</v>
+      <c r="F10" s="9">
+        <v>25</v>
       </c>
       <c r="G10" s="9">
         <v>31456.86</v>
@@ -1747,13 +1740,13 @@
         <v>24</v>
       </c>
       <c r="D11" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" s="9">
         <v>1</v>
       </c>
-      <c r="F11">
-        <v>26</v>
+      <c r="F11" s="9">
+        <v>25</v>
       </c>
       <c r="G11" s="9">
         <v>47784.48</v>
@@ -1782,13 +1775,13 @@
         <v>26</v>
       </c>
       <c r="D12" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" s="9">
         <v>1</v>
       </c>
-      <c r="F12">
-        <v>26</v>
+      <c r="F12" s="9">
+        <v>25</v>
       </c>
       <c r="G12" s="9">
         <v>51891.9</v>
@@ -1817,13 +1810,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" s="9">
         <v>1</v>
       </c>
-      <c r="F13">
-        <v>26</v>
+      <c r="F13" s="9">
+        <v>25</v>
       </c>
       <c r="G13" s="9">
         <v>27502.3</v>
@@ -1852,13 +1845,13 @@
         <v>30</v>
       </c>
       <c r="D14" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="9">
         <v>1</v>
       </c>
-      <c r="F14">
-        <v>26</v>
+      <c r="F14" s="9">
+        <v>25</v>
       </c>
       <c r="G14" s="9">
         <v>35255.54</v>
@@ -1887,13 +1880,13 @@
         <v>32</v>
       </c>
       <c r="D15" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="9">
         <v>1</v>
       </c>
-      <c r="F15">
-        <v>26</v>
+      <c r="F15" s="9">
+        <v>25</v>
       </c>
       <c r="G15" s="9">
         <v>70643.2</v>
@@ -1922,13 +1915,13 @@
         <v>34</v>
       </c>
       <c r="D16" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="9">
         <v>1</v>
       </c>
-      <c r="F16">
-        <v>26</v>
+      <c r="F16" s="9">
+        <v>25</v>
       </c>
       <c r="G16" s="9">
         <v>57220.92</v>
@@ -1957,13 +1950,13 @@
         <v>36</v>
       </c>
       <c r="D17" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="9">
         <v>1</v>
       </c>
-      <c r="F17">
-        <v>26</v>
+      <c r="F17" s="9">
+        <v>25</v>
       </c>
       <c r="G17" s="9">
         <v>180512.64</v>
@@ -1992,13 +1985,13 @@
         <v>38</v>
       </c>
       <c r="D18" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="9">
         <v>1</v>
       </c>
-      <c r="F18">
-        <v>26</v>
+      <c r="F18" s="9">
+        <v>25</v>
       </c>
       <c r="G18" s="9">
         <v>212828.16</v>
@@ -2027,13 +2020,13 @@
         <v>40</v>
       </c>
       <c r="D19" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="9">
         <v>1</v>
       </c>
-      <c r="F19">
-        <v>26</v>
+      <c r="F19" s="9">
+        <v>25</v>
       </c>
       <c r="G19" s="9">
         <v>22289.47</v>
@@ -2062,13 +2055,13 @@
         <v>42</v>
       </c>
       <c r="D20" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="9">
         <v>1</v>
       </c>
-      <c r="F20">
-        <v>26</v>
+      <c r="F20" s="9">
+        <v>25</v>
       </c>
       <c r="G20" s="9">
         <v>130809.07</v>
@@ -2097,13 +2090,13 @@
         <v>44</v>
       </c>
       <c r="D21" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" s="9">
         <v>1</v>
       </c>
-      <c r="F21">
-        <v>26</v>
+      <c r="F21" s="9">
+        <v>25</v>
       </c>
       <c r="G21" s="9">
         <v>108843.65</v>
@@ -2132,13 +2125,13 @@
         <v>46</v>
       </c>
       <c r="D22" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="9">
         <v>1</v>
       </c>
-      <c r="F22">
-        <v>26</v>
+      <c r="F22" s="9">
+        <v>25</v>
       </c>
       <c r="G22" s="9">
         <v>14097.22</v>
@@ -2167,13 +2160,13 @@
         <v>48</v>
       </c>
       <c r="D23" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="9">
         <v>1</v>
       </c>
-      <c r="F23">
-        <v>26</v>
+      <c r="F23" s="9">
+        <v>25</v>
       </c>
       <c r="G23" s="9">
         <v>180313.25</v>
@@ -2202,13 +2195,13 @@
         <v>50</v>
       </c>
       <c r="D24" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="9">
         <v>1</v>
       </c>
-      <c r="F24">
-        <v>26</v>
+      <c r="F24" s="9">
+        <v>25</v>
       </c>
       <c r="G24" s="9">
         <v>185886.58</v>
@@ -2237,13 +2230,13 @@
         <v>52</v>
       </c>
       <c r="D25" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="9">
         <v>1</v>
       </c>
-      <c r="F25">
-        <v>26</v>
+      <c r="F25" s="9">
+        <v>25</v>
       </c>
       <c r="G25" s="9">
         <v>13472.48</v>
@@ -2272,13 +2265,13 @@
         <v>54</v>
       </c>
       <c r="D26" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" s="9">
         <v>1</v>
       </c>
-      <c r="F26">
-        <v>26</v>
+      <c r="F26" s="9">
+        <v>25</v>
       </c>
       <c r="G26" s="9">
         <v>50054.18</v>
